--- a/sap api.xlsx
+++ b/sap api.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SAP\SAP_Monitoring_System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956E345B-64E6-44D8-9520-77083F719ADD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8544D52A-29F9-4687-8921-229A7101FE0E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{6290779B-7ADC-4AF5-888D-C8DF0032F89E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
   <si>
     <t>Sr. No</t>
   </si>
@@ -166,6 +166,66 @@
   </si>
   <si>
     <t>WEBDISPATCHER URL</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_lock_user/lockedusers?sap-client=100</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_inact_user/inactiveusers?sap-client=100</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_priv_user/highprivusers?sap-client=100</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_unused_roles/unusedroles?sap-client=100</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_ghost_roles/ghostroles?sap-client=100</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_unused_profil/unusedprofiles?sap-client=100</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_unused_tcodes/unusedtcodes?sap-client=100</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_redudant_role/redudantroles?sap-client=100</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_empty_shell/emptyshell?sap-client=100</t>
+  </si>
+  <si>
+    <t>Locked Users</t>
+  </si>
+  <si>
+    <t>Inactive Users (Users did not login from last 30 days)</t>
+  </si>
+  <si>
+    <t>High Prev Users (User having SAP_ALL and SAP_NEW)</t>
+  </si>
+  <si>
+    <t>Un-Assigned Roles</t>
+  </si>
+  <si>
+    <t>Un-Used Roles (Roles which are assigned to Users, but not used by user in last 30 days)</t>
+  </si>
+  <si>
+    <t>Un-Used Profiles</t>
+  </si>
+  <si>
+    <t>Un-used tcodes</t>
+  </si>
+  <si>
+    <t>Un-deleted users ( HR Master status is Employee Retired or Left, but SAP User ID exists in the system)</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_undeleted_usr/undeletedusers?sap-client=100</t>
+  </si>
+  <si>
+    <t>Redudant single roles (Composite Roles with Redundant Single Roles)</t>
+  </si>
+  <si>
+    <t>Expired Roles or No Roles assigned to Valid User</t>
   </si>
 </sst>
 </file>
@@ -233,7 +293,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -246,6 +306,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -561,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC83FB5-3B55-4A03-8A31-296AAB5E9A7A}">
-  <dimension ref="B2:D26"/>
+  <dimension ref="B2:D36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="26.1796875" customWidth="1"/>
@@ -841,6 +904,116 @@
       </c>
       <c r="D26" s="5" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B27" s="4">
+        <v>25</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B28" s="4">
+        <v>26</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B29" s="4">
+        <v>27</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B30" s="4">
+        <v>28</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B31" s="4">
+        <v>29</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B32" s="4">
+        <v>30</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B33" s="4">
+        <v>31</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B34" s="4">
+        <v>32</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B35" s="4">
+        <v>33</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="4">
+        <v>34</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -869,6 +1042,16 @@
     <hyperlink ref="D24" r:id="rId22" xr:uid="{F3508B28-552E-4731-B2D4-4D6C03FEF13B}"/>
     <hyperlink ref="D25" r:id="rId23" location="Shell-home" xr:uid="{FC419D54-450F-4183-AD25-53B307FF9969}"/>
     <hyperlink ref="D26" r:id="rId24" xr:uid="{3F892F10-D955-4110-9906-A2D64B705959}"/>
+    <hyperlink ref="D27" r:id="rId25" xr:uid="{DCAC7F1D-90FF-4314-BECA-C23CAF00F23D}"/>
+    <hyperlink ref="D28" r:id="rId26" xr:uid="{C0C75FFB-08A5-4A5D-961A-C8C3E2626FC5}"/>
+    <hyperlink ref="D29" r:id="rId27" xr:uid="{B432CCEF-017A-496E-B6B1-4E1FBAEBD71F}"/>
+    <hyperlink ref="D30" r:id="rId28" xr:uid="{E69BA9BC-A4DE-48AE-92CD-E816F5ACA23B}"/>
+    <hyperlink ref="D31" r:id="rId29" xr:uid="{11F3CCD7-8E67-42F3-829C-CD138B095D94}"/>
+    <hyperlink ref="D32" r:id="rId30" xr:uid="{E1CF85B7-3D17-4301-AA00-118C27977870}"/>
+    <hyperlink ref="D33" r:id="rId31" xr:uid="{B8AB806B-F993-4A68-A9AD-D7036FF2517D}"/>
+    <hyperlink ref="D34" r:id="rId32" xr:uid="{1C601621-7C76-4394-BE00-B1367F43FD3B}"/>
+    <hyperlink ref="D35" r:id="rId33" xr:uid="{00C5BB1D-97B4-4E6A-AB67-2C89407364DE}"/>
+    <hyperlink ref="D36" r:id="rId34" xr:uid="{7E483AE6-A5F8-42DA-B0BE-D1166A4A4FF9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/sap api.xlsx
+++ b/sap api.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SAP\SAP_Monitoring_System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8544D52A-29F9-4687-8921-229A7101FE0E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B871A5-7712-4814-B2EA-2A5410598985}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{6290779B-7ADC-4AF5-888D-C8DF0032F89E}"/>
   </bookViews>

--- a/sap api.xlsx
+++ b/sap api.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SAP\SAP_Monitoring_System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B871A5-7712-4814-B2EA-2A5410598985}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B4A983-F1B4-4A8D-AACD-219DD69EFAC0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{6290779B-7ADC-4AF5-888D-C8DF0032F89E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="100" sheetId="1" r:id="rId1"/>
+    <sheet name="150" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="70">
   <si>
     <t>Sr. No</t>
   </si>
@@ -226,6 +227,15 @@
   </si>
   <si>
     <t>Expired Roles or No Roles assigned to Valid User</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_log_vol_srv/log_volume?sap-client=150</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_st22_err_srv/st22_errors?sap-client=150</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_lock_user/lockedusers?sap-client=150</t>
   </si>
 </sst>
 </file>
@@ -642,7 +652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -1018,7 +1028,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_data_vol_srv/data_volume?sap-client=100" xr:uid="{D458805C-EB25-4152-94DF-46E970571AB9}"/>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{D458805C-EB25-4152-94DF-46E970571AB9}"/>
     <hyperlink ref="D4" r:id="rId2" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_log_vol_srv/log_volume?sap-client=100" xr:uid="{E4DDF5E8-DE18-4E59-A73F-5FFE71C58B2B}"/>
     <hyperlink ref="D5" r:id="rId3" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_st22_err_srv/st22_errors?sap-client=100" xr:uid="{AF884513-815F-4F77-9FBF-4D70A08FB9DF}"/>
     <hyperlink ref="D6" r:id="rId4" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_backup_srv/backup?sap-client=150" xr:uid="{FC986B2D-E1AA-4F96-B0CE-8294997A3C6F}"/>
@@ -1055,4 +1065,325 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0DB1DD-137F-4B15-8C31-FF822AD09832}">
+  <dimension ref="B2:C35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="93.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B24" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="B27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="B28" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="B29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" ht="174" x14ac:dyDescent="0.35">
+      <c r="B30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="B31" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="B32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="B33" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="B34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="B35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{295A7FFC-71F7-4839-A93B-C41C414CF84A}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{6C287CC0-2D76-4064-9859-A4621BCB7BE6}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{11355D3F-2CFA-40FE-ADD7-A9139F848D16}"/>
+    <hyperlink ref="C5" r:id="rId4" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_backup_srv/backup?sap-client=150" xr:uid="{66F5EFA0-454D-4BD6-8C4B-1174552DFB80}"/>
+    <hyperlink ref="C6" r:id="rId5" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_sm13_upd_srv/update?sap-client=150" xr:uid="{7C21BD9E-17A0-4AE3-BB2A-5A44EA26B7A1}"/>
+    <hyperlink ref="C7" r:id="rId6" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_sm12_lock_srv/locks?sap-client=150" xr:uid="{1ACCB033-8220-402E-81B3-5372ABBB46AD}"/>
+    <hyperlink ref="C8" r:id="rId7" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_sm51_statesrv/sm51?sap-client=150" xr:uid="{29432494-2C4A-4B8D-8E9E-E34C4964E772}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{DA6F1CBC-8A92-4CCD-8B13-868B5AF57831}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{9F9F9E2F-8945-4C5A-90F6-A70E6144236E}"/>
+    <hyperlink ref="C11" r:id="rId10" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_st06_data_srv/st06?sap-client=150" xr:uid="{86B25CBE-DD30-4E11-9078-BAA6F15D9196}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{FEC71B07-B84E-4B67-B9EF-F40AB2B64374}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{CCD0E19D-C4E9-4889-A622-B1C9FCAE5551}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{2DB8FCA8-2B20-4868-832D-81E17EB495A7}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{6A05A91D-BE4A-4817-B493-3768089E97EA}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{33D2B5C9-5C2B-4F04-969A-1D35172052F9}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{604D7667-134F-4F9B-93A2-F6BAEF244323}"/>
+    <hyperlink ref="C18" r:id="rId17" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_st06_data_srv/st06?sap-client=150" xr:uid="{5560ECE3-3669-4684-ABFC-D6DD20B55ED5}"/>
+    <hyperlink ref="C19" r:id="rId18" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_data_vol_srv/data_volume?sap-client=150" xr:uid="{B399B566-889B-4A6C-8495-99390D5DBE72}"/>
+    <hyperlink ref="C20" r:id="rId19" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_data_vol_srv/data_volume?sap-client=150" display="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_data_vol_srv/data_volume?sap-client=150" xr:uid="{33E39A6B-3AC5-41CB-9107-6A0F62A5C962}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{CBECFC64-2DE5-4D73-AB72-CF19FF1062C8}"/>
+    <hyperlink ref="C22" r:id="rId21" xr:uid="{15B2553A-EE5A-4026-8CF9-E0B5DF151D2F}"/>
+    <hyperlink ref="C23" r:id="rId22" xr:uid="{B1E927A5-281D-4B7E-A814-6F23934BECDF}"/>
+    <hyperlink ref="C24" r:id="rId23" location="Shell-home" xr:uid="{C3B6801C-3E5B-4B07-B4C0-6F1B7D0812B0}"/>
+    <hyperlink ref="C25" r:id="rId24" xr:uid="{A77841A9-7610-46CE-8DAD-D3B6FAB70359}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{2FB462AD-6D43-46DC-9A4E-A73A5B10A433}"/>
+    <hyperlink ref="C27" r:id="rId26" xr:uid="{80D9C6B0-E8A3-4E70-9B0B-90EA102E4FF1}"/>
+    <hyperlink ref="C28" r:id="rId27" xr:uid="{94A89655-B174-4931-AB02-5CB36A18185E}"/>
+    <hyperlink ref="C29" r:id="rId28" xr:uid="{A3ED5A5F-2BDA-4232-AA85-502CFC11D6B2}"/>
+    <hyperlink ref="C30" r:id="rId29" xr:uid="{5FF4C650-8018-4199-AA03-53A94608AC4B}"/>
+    <hyperlink ref="C31" r:id="rId30" xr:uid="{AD516B66-D4BA-47F5-A2E9-929AD087E8DA}"/>
+    <hyperlink ref="C32" r:id="rId31" xr:uid="{0E2F74D5-2B54-43C9-AB40-63A706826756}"/>
+    <hyperlink ref="C33" r:id="rId32" xr:uid="{E5B5ABBA-3BBE-4023-91BA-B22480EE0D7E}"/>
+    <hyperlink ref="C34" r:id="rId33" xr:uid="{493DAD06-2FDF-4001-A9E1-BFC71C8E606A}"/>
+    <hyperlink ref="C35" r:id="rId34" xr:uid="{A93882C6-B4C6-4E09-A266-52175D836735}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>